--- a/Bestmarken.xlsx
+++ b/Bestmarken.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E033076-A4A8-48D2-B83A-EBF0037AB97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EA203E-35A0-41D0-BC5E-3419ECE1FCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A2B06356-C46F-4856-9278-6D1C231CCE28}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="64">
   <si>
     <t>All-time-best</t>
   </si>
@@ -235,8 +235,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -304,10 +304,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1767,11 +1767,13 @@
       <c r="C42" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
-      <c r="G42" s="8">
-        <v>45565</v>
+      <c r="G42" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>41</v>
